--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487577_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487577_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6731</v>
+        <v>1.9996</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1907</v>
+        <v>2.0896</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4823</v>
+        <v>-0.09</v>
       </c>
       <c r="G2" t="n">
         <v>2.5561</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9991</v>
+        <v>-0.6743</v>
       </c>
       <c r="T2" t="n">
-        <v>1.227</v>
+        <v>0.1259</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2278</v>
+        <v>-0.8002</v>
       </c>
       <c r="V2" t="n">
         <v>0.894</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4816</v>
+        <v>1.7457</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2687</v>
+        <v>0.6691</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2129</v>
+        <v>1.0766</v>
       </c>
       <c r="G3" t="n">
         <v>1.0226</v>
@@ -688,13 +688,13 @@
         <v>1.3582</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.559</v>
+        <v>-1.2949</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4722</v>
+        <v>-0.0718</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0868</v>
+        <v>-1.2231</v>
       </c>
       <c r="V3" t="n">
         <v>0.6597</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6401</v>
+        <v>-0.6128</v>
       </c>
       <c r="E4" t="n">
         <v>-0.5133</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1268</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3913</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2488</v>
+        <v>-0.2215</v>
       </c>
       <c r="T4" t="n">
         <v>0.1335</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3822</v>
+        <v>-0.355</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5346</v>
+        <v>-1.3837</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4688</v>
+        <v>-1.2372</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0033</v>
+        <v>-0.1465</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5029</v>
+        <v>-3.9413</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.152</v>
+        <v>-0.2348</v>
       </c>
       <c r="I5" t="n">
-        <v>0.649</v>
+        <v>-3.7065</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3236</v>
+        <v>-1.869</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8815</v>
+        <v>1.2647</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2052</v>
+        <v>-3.1337</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8266</v>
+        <v>-2.0723</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2704</v>
+        <v>-1.4995</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5561</v>
+        <v>-0.5729</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9702</v>
+        <v>2.1344</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>-0.194</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3331</v>
+        <v>-0.4708</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6079</v>
+        <v>-0.0682</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.4026</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2716</v>
+        <v>0.894</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4477</v>
+        <v>0.894</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2362</v>
+        <v>-1.8382</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1986</v>
+        <v>0.0288</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0375</v>
+        <v>-1.8671</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.9413</v>
+        <v>-1.5029</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2348</v>
+        <v>-2.152</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.7065</v>
+        <v>0.649</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.869</v>
+        <v>0.3236</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2647</v>
+        <v>-0.8815</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.1337</v>
+        <v>1.2052</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0723</v>
+        <v>-1.8266</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4995</v>
+        <v>-1.2704</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5729</v>
+        <v>-0.5561</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.194</v>
+        <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3284</v>
+        <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3232</v>
+        <v>-0.6368</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0296</v>
+        <v>0.1679</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2936</v>
+        <v>-0.8047</v>
       </c>
       <c r="V6" t="n">
-        <v>0.894</v>
+        <v>1.2716</v>
       </c>
       <c r="W6" t="n">
-        <v>0.894</v>
+        <v>2.4477</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5924</v>
+        <v>-2.6197</v>
       </c>
       <c r="E7" t="n">
         <v>-2.5871</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0053</v>
+        <v>-0.0326</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2642</v>
@@ -1000,13 +1000,13 @@
         <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.552</v>
+        <v>-0.5793</v>
       </c>
       <c r="T7" t="n">
         <v>-0.3028</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2492</v>
+        <v>-0.2765</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7073</v>
+        <v>-3.418</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6401</v>
+        <v>-1.9637</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0672</v>
+        <v>-1.4543</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6563</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5034</v>
+        <v>-0.2513</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1529</v>
+        <v>-0.3359</v>
       </c>
       <c r="J8" t="n">
-        <v>1.138</v>
+        <v>0.3887</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3666</v>
+        <v>0.4243</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7713</v>
+        <v>-0.0356</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7943</v>
+        <v>-0.9759</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.87</v>
+        <v>-0.6756</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9242</v>
+        <v>-0.3004</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.1045</v>
+        <v>-2.5224</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.0448</v>
+        <v>-4.0747</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9403</v>
+        <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7714</v>
+        <v>-2.1442</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7608</v>
+        <v>-0.3957</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-1.7485</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2821</v>
+        <v>1.8358</v>
       </c>
       <c r="W8" t="n">
-        <v>1.506</v>
+        <v>2.1179</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0275</v>
+        <v>-3.7191</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4642</v>
+        <v>-2.2514</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5633</v>
+        <v>-1.4677</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-3.3241</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2513</v>
+        <v>-3.5393</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3359</v>
+        <v>0.2152</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3887</v>
+        <v>-1.2582</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4243</v>
+        <v>-2.4633</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0356</v>
+        <v>1.2052</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9759</v>
+        <v>-2.066</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6756</v>
+        <v>-1.076</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3004</v>
+        <v>-0.99</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.5224</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.0747</v>
+        <v>-2.1344</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5523</v>
+        <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.7537</v>
+        <v>-1.289</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8962</v>
+        <v>-0.3648</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.8575</v>
+        <v>-0.9241</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8358</v>
+        <v>0.894</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1179</v>
+        <v>1.506</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.08</v>
+        <v>-4.3301</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6123</v>
+        <v>-1.7807</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4677</v>
+        <v>-2.5494</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3241</v>
+        <v>-1.6563</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.5393</v>
+        <v>-0.5034</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2152</v>
+        <v>-1.1529</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2582</v>
+        <v>1.138</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.4633</v>
+        <v>0.3666</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2052</v>
+        <v>0.7713</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.066</v>
+        <v>-2.7943</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.076</v>
+        <v>-0.87</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.99</v>
+        <v>-1.9242</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-3.1045</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1344</v>
+        <v>-5.0448</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6498</v>
+        <v>0.1486</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7257</v>
+        <v>0.6202</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9241</v>
+        <v>-0.4716</v>
       </c>
       <c r="V10" t="n">
-        <v>0.894</v>
+        <v>0.2821</v>
       </c>
       <c r="W10" t="n">
         <v>1.506</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6119</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3756</v>
+        <v>-4.5598</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7163</v>
+        <v>-2.955</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6593</v>
+        <v>-1.6048</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2912</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0262</v>
+        <v>-1.2104</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8356</v>
+        <v>-0.0743</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1906</v>
+        <v>-1.1361</v>
       </c>
       <c r="V11" t="n">
         <v>-0.894</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.039</v>
+        <v>-18.7361</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.8037</v>
+        <v>-10.5009</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.235199999999999</v>
+        <v>-8.235399999999998</v>
       </c>
       <c r="G12" t="n">
         <v>-10.3798</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.236800000000001</v>
+        <v>-6.2368</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.143299999999999</v>
+        <v>-4.1433</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4868000000000004</v>
+        <v>-0.4868</v>
       </c>
       <c r="K12" t="n">
         <v>1.3761</v>
@@ -1372,13 +1372,13 @@
         <v>-1.8627</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.8934</v>
+        <v>-9.893399999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.6127</v>
+        <v>-7.612700000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.280599999999999</v>
+        <v>-2.2806</v>
       </c>
       <c r="P12" t="n">
         <v>-5.8209</v>
@@ -1390,22 +1390,22 @@
         <v>14.5524</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.6753</v>
+        <v>-8.3726</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5329</v>
+        <v>-0.2300999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.142200000000001</v>
+        <v>-8.1424</v>
       </c>
       <c r="V12" t="n">
-        <v>5.837200000000001</v>
+        <v>5.8372</v>
       </c>
       <c r="W12" t="n">
         <v>10.5895</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.752199999999999</v>
+        <v>-4.7522</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.7639</v>
+        <v>7.8071</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6841</v>
+        <v>6.4849</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0798</v>
+        <v>1.3223</v>
       </c>
       <c r="G13" t="n">
         <v>6.3234</v>
@@ -1468,13 +1468,13 @@
         <v>2.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4118</v>
+        <v>0.6314</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2165</v>
+        <v>0.5843</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1954</v>
+        <v>0.0471</v>
       </c>
       <c r="V13" t="n">
         <v>-0.894</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2195</v>
+        <v>3.555</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9559</v>
+        <v>3.1551</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2636</v>
+        <v>0.3999</v>
       </c>
       <c r="G14" t="n">
         <v>2.5621</v>
@@ -1546,13 +1546,13 @@
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>1.135</v>
+        <v>0.4705</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5421</v>
+        <v>0.7413</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4071</v>
+        <v>-0.2708</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2239</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5134</v>
+        <v>1.9982</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4805</v>
+        <v>1.3602</v>
       </c>
       <c r="F15" t="n">
-        <v>4.9939</v>
+        <v>0.638</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5076000000000001</v>
+        <v>0.2791</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5083</v>
+        <v>-0.0634</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.016</v>
+        <v>0.3426</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1962</v>
+        <v>0.5137</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0701</v>
+        <v>0.4325</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2662</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6885</v>
+        <v>-0.2346</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4383</v>
+        <v>-0.496</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2502</v>
+        <v>0.2614</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8806</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7164</v>
+        <v>0.9702</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5733</v>
+        <v>0.7489</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3142</v>
+        <v>0.8465</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2591</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0708</v>
+        <v>1.8043</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7357</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3351</v>
+        <v>1.1687</v>
       </c>
       <c r="G16" t="n">
         <v>0.9678</v>
@@ -1702,13 +1702,13 @@
         <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4612</v>
+        <v>1.1948</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8501</v>
+        <v>0.75</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6111</v>
+        <v>0.4447</v>
       </c>
       <c r="V16" t="n">
         <v>0.6119</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5644</v>
+        <v>1.4661</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0599</v>
+        <v>-0.2636</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5044999999999999</v>
+        <v>1.7297</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2791</v>
+        <v>-0.1229</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0634</v>
+        <v>-0.1812</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3426</v>
+        <v>0.0584</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5137</v>
+        <v>-0.0771</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4325</v>
+        <v>0.3872</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.4643</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2346</v>
+        <v>-0.0458</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.496</v>
+        <v>-0.5685</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2614</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3152</v>
+        <v>0.8129</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5462</v>
+        <v>0.5016</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.231</v>
+        <v>0.3113</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9384</v>
+        <v>1.3884</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7641</v>
+        <v>0.1239</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7025</v>
+        <v>1.2645</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1229</v>
+        <v>-0.7652</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1812</v>
+        <v>0.4416</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0584</v>
+        <v>-1.2068</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0771</v>
+        <v>-1.0417</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3872</v>
+        <v>0.1483</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4643</v>
+        <v>-1.1901</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0458</v>
+        <v>0.2766</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5685</v>
+        <v>0.2933</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5227000000000001</v>
+        <v>-0.0167</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7761</v>
+        <v>2.3284</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>2.3284</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2851</v>
+        <v>0.155</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0011</v>
+        <v>0.2717</v>
       </c>
       <c r="U18" t="n">
-        <v>0.284</v>
+        <v>-0.1166</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9052</v>
+        <v>1.2844</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6675</v>
+        <v>-3.3824</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2376</v>
+        <v>4.6669</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2697</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0395</v>
+        <v>0.5083</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2301</v>
+        <v>-1.016</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0678</v>
+        <v>-1.1962</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1401</v>
+        <v>0.0701</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2078</v>
+        <v>-1.2662</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2019</v>
+        <v>0.6885</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1796</v>
+        <v>0.4383</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0223</v>
+        <v>0.2502</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7164</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.8806</v>
       </c>
       <c r="R19" t="n">
         <v>2.7164</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3524</v>
+        <v>2.3444</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5114</v>
+        <v>1.4123</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.159</v>
+        <v>0.9321</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.894</v>
+        <v>0.6119</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1179</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.215</v>
+        <v>1.0687</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.777</v>
+        <v>0.6675</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9919</v>
+        <v>0.4012</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7652</v>
+        <v>-1.2697</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4416</v>
+        <v>-0.0395</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2068</v>
+        <v>-1.2301</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0417</v>
+        <v>-1.0678</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1483</v>
+        <v>0.1401</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1901</v>
+        <v>-1.2078</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2766</v>
+        <v>-0.2019</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2933</v>
+        <v>-0.1796</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0167</v>
+        <v>-0.0223</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3284</v>
+        <v>2.7164</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3284</v>
+        <v>2.7164</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0184</v>
+        <v>0.5159</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6292</v>
+        <v>0.5114</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3892</v>
+        <v>0.0045</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3299</v>
+        <v>-0.894</v>
       </c>
       <c r="W20" t="n">
-        <v>0.894</v>
+        <v>1.2239</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2239</v>
+        <v>-2.1179</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0367</v>
+        <v>0.8524</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3499</v>
+        <v>0.7425</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3131</v>
+        <v>0.1099</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2485</v>
+        <v>1.3387</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1229</v>
+        <v>-0.0461</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1256</v>
+        <v>1.3848</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3497</v>
+        <v>1.129</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6189</v>
+        <v>0.6674</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7307</v>
+        <v>0.4617</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1011</v>
+        <v>0.2096</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.496</v>
+        <v>-0.7135</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3948</v>
+        <v>0.9231</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7463</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1045</v>
+        <v>-2.1344</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3582</v>
+        <v>2.1344</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7584</v>
+        <v>1.3495</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1047</v>
+        <v>0.8538</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3463</v>
+        <v>0.4958</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2239</v>
+        <v>-1.8358</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.073</v>
+        <v>0.0974</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1584</v>
+        <v>0.2498</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.1524</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3387</v>
+        <v>2.2485</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0461</v>
+        <v>1.1229</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3848</v>
+        <v>1.1256</v>
       </c>
       <c r="J22" t="n">
-        <v>1.129</v>
+        <v>2.3497</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6674</v>
+        <v>1.6189</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4617</v>
+        <v>0.7307</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2096</v>
+        <v>-0.1011</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7135</v>
+        <v>-0.496</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9231</v>
+        <v>0.3948</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1344</v>
+        <v>-3.1045</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1344</v>
+        <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4242</v>
+        <v>0.819</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0471</v>
+        <v>1.0046</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4713</v>
+        <v>-0.1856</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8358</v>
+        <v>-1.2239</v>
       </c>
       <c r="W22" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.7298</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1153</v>
+        <v>-1.6158</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0377</v>
+        <v>-1.5382</v>
       </c>
       <c r="F23" t="n">
         <v>-0.0776</v>
@@ -2248,10 +2248,10 @@
         <v>0.3881</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8008</v>
+        <v>0.3003</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1653</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="U23" t="n">
         <v>-0.3645</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>19.039</v>
+        <v>19.7062</v>
       </c>
       <c r="E24" t="n">
-        <v>8.235299999999999</v>
+        <v>8.235300000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>10.8037</v>
+        <v>11.4711</v>
       </c>
       <c r="G24" t="n">
         <v>10.3799</v>
       </c>
       <c r="H24" t="n">
-        <v>6.2368</v>
+        <v>6.236799999999999</v>
       </c>
       <c r="I24" t="n">
         <v>4.1433</v>
@@ -2326,19 +2326,19 @@
         <v>20.3734</v>
       </c>
       <c r="S24" t="n">
-        <v>8.6754</v>
+        <v>9.342600000000001</v>
       </c>
       <c r="T24" t="n">
         <v>8.142300000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5329999999999999</v>
+        <v>1.2004</v>
       </c>
       <c r="V24" t="n">
-        <v>-5.837400000000001</v>
+        <v>-5.8374</v>
       </c>
       <c r="W24" t="n">
-        <v>4.752200000000001</v>
+        <v>4.7522</v>
       </c>
       <c r="X24" t="n">
         <v>-10.5895</v>
